--- a/原始資料/二梅花開叫.xlsx
+++ b/原始資料/二梅花開叫.xlsx
@@ -128,16 +128,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -591,310 +591,322 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>開叫定義</t>
+          <t>★ 家規點力</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>2♣ = 至少5張♣ + 11-15個大牌點。如果只有5張♣，那你必須還有一個高花4張套。</t>
+          <t>本檔採用家規點力：**所有開叫點力下修 1 點、所有答叫點力上修 1 點**（聯手總點力因此維持不變）。註明「原書」者為原書印行的數值。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>★ 體系自評</t>
+          <t>開叫定義</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>原書直言：2♣ 是整個精確梅花體系中**最薄弱的一環**，尤其在雙人賽上。其強度對敵方來說像是某種阻擊叫，但反過來，我方已經越過了 1NT——很多情況下的最佳定約。問題常常出在♣套的質量上。</t>
+          <t>2♣ = 至少5張♣ + 10-14個大牌點（家規下修 1 點；原書 11-15）。如果只有5張♣，那你必須還有一個高花4張套。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>★ 體系自評</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>原書直言：2♣ 是整個精確梅花體系中**最薄弱的一環**，尤其在雙人賽上。其強度對敵方來說像是某種阻擊叫，但反過來，我方已經越過了 1NT——很多情況下的最佳定約。問題常常出在♣套的質量上。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
           <t>體系的調整</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>允許拿著5張♣和四張高花改開 1♦ 或 1NT，特別是在♣很弱的時候。</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>逼叫層級</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>2♣ 開叫後的**第一次接力（2♦）並非進局逼叫**；但如果再一次接力，就一定保證進局實力了。</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>使用限制</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>接力序列**只用於第一、二家開叫的 2♣**。第三、四家開叫時，已經 pass 過的應叫者可以在 2♦ 之後完全不採用人工接力，所有叫牌都是自然的。</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>牌型寫法</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>四位數字一律按 ♠-♥-♦-♣ 順序。例：2-2-2-7 是 7張♣。</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr"/>
-      <c r="B11" s="5" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr"/>
+      <c r="B12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>接力術語</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
         <is>
           <t>54Pick-up</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>問 5-4 牌型中那個 4 張套在哪一門、幾張。A、B 兩個分支都走這個原則。</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>問「剩下兩門怎麼分」。由平均排到極端，同程度時級別較高的那門較短排前面。</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Splinter-relay</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>問「短套在哪門」。三級，由最低級花色排到最高級。</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>Six-shooter</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>問 6 張以上單套牌的完整分佈，一次講完。只有 D 分支用得到。</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>牌型問完後問 A、K、Q 的確切位置（Colour-Rank-And-SHape）。</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr"/>
-      <c r="B18" s="5" t="inlineStr"/>
-    </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr"/>
+      <c r="B19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>本章需要留意的地方</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>C 分支不用 Six-shooter</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>因為 2NT 這個叫品已經把開叫者的♣**精確限定為 6 張**，不需要再用 Six-shooter 去問長度，直接問剩下三門怎麼分即可。這是 C 與 D 兩個分支最大的差別。</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>D 分支全程 Six-shooter</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>3♣ 只說了「至少6張♣、無邊花套、低限」，長度還沒定死，所以開叫者所有的再叫都遵從 Six-shooter 接力原則。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
+          <t>D 分支全程 Six-shooter</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>3♣ 只說了「至少6張♣、無邊花套、低限」，長度還沒定死，所以開叫者所有的再叫都遵從 Six-shooter 接力原則。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>★ 8張以上套無解</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>例2 揭露了體系的硬限制：Sidestep 只設計到 7 級答叫，**處理不了 8 張以上的套**。8221 牌型必須被當成 7321 來叫。實戰中 Glenn 自行在階梯上加了第 8 級（兩短套 0-1 分佈），書中同時警告這樣做有把定約叫得太高的風險。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr"/>
-      <c r="B23" s="5" t="inlineStr"/>
-    </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="6" t="inlineStr"/>
+      <c r="B24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>內容</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>2. 對2♣的應叫</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>應叫者的全部第一應叫及含義。</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>3. 接力主幹</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>2♣ – 2♦ 後開叫者的 12 種再叫與對應接力叫品。</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>4. A分支（2♥）</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>2♥ = 4張♥。7 種再叫，走 '54Pick-up 原則。</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>5. B分支（2♠）</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>2♠ = 4張♠。6 種再叫，走 '54Pick-up 原則。</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
         <is>
           <t>6. C分支（2NT）</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>2NT = 6張♣高限。4 種再叫。</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>7. D分支（3♣）</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>3♣ = 6張以上♣低限。7 種再叫，走 Six-shooter 原則。</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>8. 示例牌張</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>例1–例3 的持牌、局況與結果評論。</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>9. 示例叫序</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>例1–例3 的完整叫序，逐叫列出。</t>
         </is>
@@ -932,7 +944,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>2♣ – ？　（2♣ = 至少5張♣ + 11-15大牌點）</t>
+          <t>2♣ – ？　（2♣ = 至少5張♣ + 10-14大牌點）</t>
         </is>
       </c>
     </row>
@@ -978,7 +990,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>5張以上套，6-11個大牌點。</t>
+          <t>5張以上套，7-12個大牌點。</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -995,7 +1007,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>均型牌，10-12大牌點。</t>
+          <t>均型牌，11-13大牌點。</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1012,7 +1024,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>至少三張♣支持，6-9個大牌點。</t>
+          <t>至少三張♣支持，7-10個大牌點。</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -2859,7 +2871,7 @@
       </c>
       <c r="F4" s="18" t="inlineStr">
         <is>
-          <t>至少5張♣，11-15大牌點</t>
+          <t>至少5張♣，10-14大牌點</t>
         </is>
       </c>
     </row>

--- a/原始資料/二梅花開叫.xlsx
+++ b/原始資料/二梅花開叫.xlsx
@@ -14,8 +14,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5.B分支(2♠)" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6.C分支(2NT)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7.D分支(3♣)" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8.示例牌張" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.示例叫序" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -576,6 +574,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -885,30 +884,6 @@
       <c r="B31" s="7" t="inlineStr">
         <is>
           <t>3♣ = 6張以上♣低限。7 種再叫，走 Six-shooter 原則。</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>8. 示例牌張</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>例1–例3 的持牌、局況與結果評論。</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>9. 示例叫序</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>例1–例3 的完整叫序，逐叫列出。</t>
         </is>
       </c>
     </row>
@@ -2427,1252 +2402,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="66" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>叫牌示例：持牌、局況與結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>例號</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>出處</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>局況／發牌</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>方位</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>♠</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>♥</t>
-        </is>
-      </c>
-      <c r="G3" s="9" t="inlineStr">
-        <is>
-          <t>♦</t>
-        </is>
-      </c>
-      <c r="H3" s="9" t="inlineStr">
-        <is>
-          <t>♣</t>
-        </is>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
-        <is>
-          <t>最終定約</t>
-        </is>
-      </c>
-      <c r="J3" s="9" t="inlineStr">
-        <is>
-          <t>評論</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="17" t="inlineStr">
-        <is>
-          <t>例1</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>冰島公開雙人賽</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>東西有局，西發牌</t>
-        </is>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>A854</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="H4" s="20" t="inlineStr">
-        <is>
-          <t>AQJ863</t>
-        </is>
-      </c>
-      <c r="I4" s="19" t="inlineStr">
-        <is>
-          <t>6♣</t>
-        </is>
-      </c>
-      <c r="J4" s="18" t="inlineStr">
-        <is>
-          <t>走完 A 分支的標準流程：2NT 先分低限，再用 '54Pick-up 找出 4 張套，Sidestep 補完分佈，最後 CRASH 問 A、K。鐵的12墩，極好的比賽分。</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>例1</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr"/>
-      <c r="C5" s="13" t="inlineStr"/>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
-        <is>
-          <t>AK9</t>
-        </is>
-      </c>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="G5" s="21" t="inlineStr">
-        <is>
-          <t>A954</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t>K972</t>
-        </is>
-      </c>
-      <c r="I5" s="15" t="inlineStr"/>
-      <c r="J5" s="13" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="inlineStr">
-        <is>
-          <t>例2</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>1993年歐錦賽前挪威隊最後一次訓練</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>雙方無局，西發牌</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="inlineStr">
-        <is>
-          <t>AK87</t>
-        </is>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="20" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H6" s="20" t="inlineStr">
-        <is>
-          <t>QJ1087542</t>
-        </is>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>5NT</t>
-        </is>
-      </c>
-      <c r="J6" s="18" t="inlineStr">
-        <is>
-          <t>★ 揭露體系硬限制：Sidestep 只提供 7 級答叫，處理不了 8 張以上的套。8221 必須當 7321 叫；Glenn 自行加了第 8 級表示兩短套 0-1 分佈。書中警告這樣有把定約叫得太高的風險，另一個選擇是在 3♠ 後叫 4NT（加6級）顯示 4-0-2-7（稍微扭曲牌情）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>例2</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr"/>
-      <c r="C7" s="13" t="inlineStr"/>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>東 Terje</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="inlineStr">
-        <is>
-          <t>Q54</t>
-        </is>
-      </c>
-      <c r="F7" s="21" t="inlineStr">
-        <is>
-          <t>AKQ4</t>
-        </is>
-      </c>
-      <c r="G7" s="21" t="inlineStr">
-        <is>
-          <t>KQJ</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
-        <is>
-          <t>K63</t>
-        </is>
-      </c>
-      <c r="I7" s="15" t="inlineStr"/>
-      <c r="J7" s="13" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>例3</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>叫牌競賽</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>南北有局，南發牌</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F8" s="20" t="inlineStr">
-        <is>
-          <t>AK4</t>
-        </is>
-      </c>
-      <c r="G8" s="20" t="inlineStr">
-        <is>
-          <t>A109</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>KJ9853</t>
-        </is>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>7♣</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="inlineStr">
-        <is>
-          <t>C 分支一路問到底：2NT 已限定 6 張♣，3NT 一叫講完 1-3-3-6，之後三輪 CRASH 問 A、K。在 5NT 之後 Ulf 可以看出 Glenn 手裡應該是♥K和♣K。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>例3</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr"/>
-      <c r="C9" s="13" t="inlineStr"/>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E9" s="21" t="inlineStr">
-        <is>
-          <t>AQ10952</t>
-        </is>
-      </c>
-      <c r="F9" s="21" t="inlineStr">
-        <is>
-          <t>Q8</t>
-        </is>
-      </c>
-      <c r="G9" s="21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H9" s="21" t="inlineStr">
-        <is>
-          <t>AQ72</t>
-        </is>
-      </c>
-      <c r="I9" s="15" t="inlineStr"/>
-      <c r="J9" s="13" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>例3 標示「南發牌」但由西家（Glenn）開叫 2♣，即南家先 pass——照原文保留。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A11:J11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F44"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="66" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>叫牌示例：完整叫序（逐叫）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>例號</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="inlineStr">
-        <is>
-          <t>局況</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>序號</t>
-        </is>
-      </c>
-      <c r="D3" s="9" t="inlineStr">
-        <is>
-          <t>叫者</t>
-        </is>
-      </c>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>叫品</t>
-        </is>
-      </c>
-      <c r="F3" s="9" t="inlineStr">
-        <is>
-          <t>說明</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>例1</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>東西有局，西發牌</t>
-        </is>
-      </c>
-      <c r="C4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E4" s="17" t="inlineStr">
-        <is>
-          <t>2♣</t>
-        </is>
-      </c>
-      <c r="F4" s="18" t="inlineStr">
-        <is>
-          <t>至少5張♣，10-14大牌點</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="23" t="inlineStr"/>
-      <c r="B5" s="13" t="inlineStr"/>
-      <c r="C5" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>2♦</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="inlineStr">
-        <is>
-          <t>接力扳機</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="24" t="inlineStr"/>
-      <c r="B6" s="11" t="inlineStr"/>
-      <c r="C6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E6" s="10" t="inlineStr">
-        <is>
-          <t>2♥</t>
-        </is>
-      </c>
-      <c r="F6" s="11" t="inlineStr">
-        <is>
-          <t>4張♥ → 進 A 分支</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="inlineStr"/>
-      <c r="B7" s="13" t="inlineStr"/>
-      <c r="C7" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>2♠</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>'54Pick-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="24" t="inlineStr"/>
-      <c r="B8" s="11" t="inlineStr"/>
-      <c r="C8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E8" s="10" t="inlineStr">
-        <is>
-          <t>2NT</t>
-        </is>
-      </c>
-      <c r="F8" s="11" t="inlineStr">
-        <is>
-          <t>低限開叫</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="inlineStr"/>
-      <c r="B9" s="13" t="inlineStr"/>
-      <c r="C9" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>3♣</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="inlineStr">
-        <is>
-          <t>'54Pick-up（低限確認後再問牌型）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="24" t="inlineStr"/>
-      <c r="B10" s="11" t="inlineStr"/>
-      <c r="C10" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E10" s="10" t="inlineStr">
-        <is>
-          <t>3♦</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
-        <is>
-          <t>6張以上♣ + 4張♥</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="inlineStr"/>
-      <c r="B11" s="13" t="inlineStr"/>
-      <c r="C11" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>3♥</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="inlineStr">
-        <is>
-          <t>Sidestep</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="24" t="inlineStr"/>
-      <c r="B12" s="11" t="inlineStr"/>
-      <c r="C12" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E12" s="10" t="inlineStr">
-        <is>
-          <t>3♠</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
-        <is>
-          <t>1-4-2-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="inlineStr"/>
-      <c r="B13" s="13" t="inlineStr"/>
-      <c r="C13" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>4♣</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="inlineStr"/>
-      <c r="B14" s="11" t="inlineStr"/>
-      <c r="C14" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>5♣</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
-        <is>
-          <t>2個A，♠+♦ 或 ♥+♣（Shape 類）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="inlineStr"/>
-      <c r="B15" s="13" t="inlineStr"/>
-      <c r="C15" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>5♦</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="inlineStr"/>
-      <c r="B16" s="11" t="inlineStr"/>
-      <c r="C16" s="14" t="n">
-        <v>13</v>
-      </c>
-      <c r="D16" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E16" s="10" t="inlineStr">
-        <is>
-          <t>5♥</t>
-        </is>
-      </c>
-      <c r="F16" s="11" t="inlineStr">
-        <is>
-          <t>沒有K</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="inlineStr"/>
-      <c r="B17" s="13" t="inlineStr"/>
-      <c r="C17" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>6♣</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>鐵的12墩，極好的比賽分</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="inlineStr">
-        <is>
-          <t>註：A 分支的教科書式跑法：先分限、再找 4 張套、再補分佈、最後問大牌。</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="inlineStr">
-        <is>
-          <t>例2</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>雙方無局，西發牌</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E20" s="17" t="inlineStr">
-        <is>
-          <t>2♣</t>
-        </is>
-      </c>
-      <c r="F20" s="18" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="23" t="inlineStr"/>
-      <c r="B21" s="13" t="inlineStr"/>
-      <c r="C21" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>東 Terje</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>2♦</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>接力扳機</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="24" t="inlineStr"/>
-      <c r="B22" s="11" t="inlineStr"/>
-      <c r="C22" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E22" s="10" t="inlineStr">
-        <is>
-          <t>2♠</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr">
-        <is>
-          <t>4張♠ → 進 B 分支</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="23" t="inlineStr"/>
-      <c r="B23" s="13" t="inlineStr"/>
-      <c r="C23" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>東 Terje</t>
-        </is>
-      </c>
-      <c r="E23" s="12" t="inlineStr">
-        <is>
-          <t>2NT</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>'54Pick-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="24" t="inlineStr"/>
-      <c r="B24" s="11" t="inlineStr"/>
-      <c r="C24" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E24" s="10" t="inlineStr">
-        <is>
-          <t>3♣</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr">
-        <is>
-          <t>低限開叫</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="23" t="inlineStr"/>
-      <c r="B25" s="13" t="inlineStr"/>
-      <c r="C25" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>東 Terje</t>
-        </is>
-      </c>
-      <c r="E25" s="12" t="inlineStr">
-        <is>
-          <t>3♦</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="inlineStr">
-        <is>
-          <t>'54Pick-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr"/>
-      <c r="B26" s="11" t="inlineStr"/>
-      <c r="C26" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E26" s="10" t="inlineStr">
-        <is>
-          <t>3♥</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>6張以上♣ + 4張♠</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="inlineStr"/>
-      <c r="B27" s="13" t="inlineStr"/>
-      <c r="C27" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>東 Terje</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>3♠</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="inlineStr">
-        <is>
-          <t>Sidestep</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="24" t="inlineStr"/>
-      <c r="B28" s="11" t="inlineStr"/>
-      <c r="C28" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>5♦</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>4-0-1-8 ← 自行加到第 8 級（兩短套 0-1）</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="23" t="inlineStr"/>
-      <c r="B29" s="13" t="inlineStr"/>
-      <c r="C29" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>東 Terje</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>5♥</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="24" t="inlineStr"/>
-      <c r="B30" s="11" t="inlineStr"/>
-      <c r="C30" s="14" t="n">
-        <v>11</v>
-      </c>
-      <c r="D30" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E30" s="10" t="inlineStr">
-        <is>
-          <t>5NT</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>1個A</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="23" t="inlineStr"/>
-      <c r="B31" s="13" t="inlineStr"/>
-      <c r="C31" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>東 Terje</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="25" t="inlineStr">
-        <is>
-          <t>註：★ Sidestep 只有 7 級，裝不下 8 張套。Glenn 自行加一級表示 0-1，第 9 級則表示 1-0。替代方案：3♠ 後叫 4NT（加6級）顯示 4-0-2-7。另外，Terje 其實可以在 3♣ 後直接叫 3NT 止叫——但 Glenn 會繼續叫 4♣（逼叫），因為取消絕對止叫等於宣告自己是 8-4 這種極端牌型。</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
-        <is>
-          <t>例3</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>南北有局，南發牌（南先 pass，由西家開叫）</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>2♣</t>
-        </is>
-      </c>
-      <c r="F34" s="18" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="23" t="inlineStr"/>
-      <c r="B35" s="13" t="inlineStr"/>
-      <c r="C35" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E35" s="12" t="inlineStr">
-        <is>
-          <t>2♦</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="inlineStr">
-        <is>
-          <t>接力扳機</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="24" t="inlineStr"/>
-      <c r="B36" s="11" t="inlineStr"/>
-      <c r="C36" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="D36" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E36" s="10" t="inlineStr">
-        <is>
-          <t>2NT</t>
-        </is>
-      </c>
-      <c r="F36" s="11" t="inlineStr">
-        <is>
-          <t>6張♣，高限無邊花套 → 進 C 分支</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="23" t="inlineStr"/>
-      <c r="B37" s="13" t="inlineStr"/>
-      <c r="C37" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D37" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>3♣</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="inlineStr">
-        <is>
-          <t>接力</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="24" t="inlineStr"/>
-      <c r="B38" s="11" t="inlineStr"/>
-      <c r="C38" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="D38" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E38" s="10" t="inlineStr">
-        <is>
-          <t>3NT</t>
-        </is>
-      </c>
-      <c r="F38" s="11" t="inlineStr">
-        <is>
-          <t>1-3-3-6</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="23" t="inlineStr"/>
-      <c r="B39" s="13" t="inlineStr"/>
-      <c r="C39" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D39" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>4♣</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="24" t="inlineStr"/>
-      <c r="B40" s="11" t="inlineStr"/>
-      <c r="C40" s="14" t="n">
-        <v>7</v>
-      </c>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>4♠</t>
-        </is>
-      </c>
-      <c r="F40" s="11" t="inlineStr">
-        <is>
-          <t>同色2A</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="inlineStr"/>
-      <c r="B41" s="13" t="inlineStr"/>
-      <c r="C41" s="15" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>4NT</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="inlineStr"/>
-      <c r="B42" s="11" t="inlineStr"/>
-      <c r="C42" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="D42" s="14" t="inlineStr">
-        <is>
-          <t>西 Glenn</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>5NT</t>
-        </is>
-      </c>
-      <c r="F42" s="11" t="inlineStr">
-        <is>
-          <t>2個K，♠+♦ 或 ♥+♣（Shape 類）</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="23" t="inlineStr"/>
-      <c r="B43" s="13" t="inlineStr"/>
-      <c r="C43" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D43" s="15" t="inlineStr">
-        <is>
-          <t>東 Ulf</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>7♣</t>
-        </is>
-      </c>
-      <c r="F43" s="13" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="25" t="inlineStr">
-        <is>
-          <t>註：C 分支只花兩叫就問完牌型（2NT 已限定 6 張♣，3NT 補完剩下三門），空間全部留給 CRASH。原書附註：不贊同把 ♠K ♥AXX ♦AKX ♣JXXXXX 當高限開叫，但就算真是這樣，只要捉住♣K定約也能做成。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A32:F32"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/原始資料/二梅花開叫.xlsx
+++ b/原始資料/二梅花開叫.xlsx
@@ -574,7 +574,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1548,7 +1547,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>高限開叫</t>
+          <t>低限開叫</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -1705,10 +1704,11 @@
       </c>
       <c r="E11" s="11" t="inlineStr"/>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>第一級 2NT 只回答「我是高限」，牌型留到下一次接力再問——這是 5-4 型牌力範圍較寬時的標準處理（見第三章）。</t>
+          <t>第一級 2NT 只回答「我是低限」，牌型留到下一次接力再問——這是 5-4 型牌力範圍較寬時的標準處理（見第三章）。</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>高限開叫</t>
+          <t>低限開叫</t>
         </is>
       </c>
       <c r="C5" s="14" t="inlineStr">
@@ -1937,6 +1937,7 @@
       </c>
       <c r="E10" s="13" t="inlineStr"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
